--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488099_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488099_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1431</v>
+        <v>3.2908</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9659</v>
+        <v>5.1136</v>
       </c>
       <c r="F2" t="n">
         <v>-1.8228</v>
@@ -610,10 +610,10 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1982</v>
+        <v>-0.0505</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0696</v>
+        <v>0.0781</v>
       </c>
       <c r="U2" t="n">
         <v>-0.1286</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3863</v>
+        <v>0.7139</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.0494</v>
+        <v>-0.8622</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4357</v>
+        <v>1.5761</v>
       </c>
       <c r="G3" t="n">
         <v>-1.6471</v>
@@ -688,13 +688,13 @@
         <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3542</v>
+        <v>-0.0266</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6312</v>
+        <v>-0.444</v>
       </c>
       <c r="U3" t="n">
-        <v>0.277</v>
+        <v>0.4174</v>
       </c>
       <c r="V3" t="n">
         <v>0.6036</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>E. DOMENECH ANTE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3417</v>
+        <v>0.5266999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6352</v>
+        <v>-0.9678</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2936</v>
+        <v>1.4945</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1104</v>
+        <v>1.6085</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1545</v>
+        <v>-0.7008</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0441</v>
+        <v>2.3093</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7753</v>
+        <v>2.3639</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6949</v>
+        <v>0.0945</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0804</v>
+        <v>2.2694</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.6648</v>
+        <v>-0.7554</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5404</v>
+        <v>-0.7953</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1244</v>
+        <v>0.0399</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9911</v>
+        <v>-1.784</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.9645</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9911</v>
+        <v>2.1805</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3274</v>
+        <v>0.1238</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0696</v>
+        <v>-0.5743</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2577</v>
+        <v>0.6982</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4325</v>
+        <v>0.5784</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.0704</v>
+        <v>1.2071</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3621</v>
+        <v>-0.6287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. DOMENECH ANTE</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0813</v>
+        <v>0.3231</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.8286</v>
+        <v>1.392</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7472</v>
+        <v>-1.0689</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6085</v>
+        <v>0.1104</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7008</v>
+        <v>0.1545</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3093</v>
+        <v>-0.0441</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3639</v>
+        <v>1.7753</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0945</v>
+        <v>1.6949</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2694</v>
+        <v>0.0804</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7554</v>
+        <v>-1.6648</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7953</v>
+        <v>-1.5404</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0399</v>
+        <v>-0.1244</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.784</v>
+        <v>0.9911</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1805</v>
+        <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4843</v>
+        <v>-0.3459</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4351</v>
+        <v>-0.3128</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9509</v>
+        <v>-0.0331</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5784</v>
+        <v>-0.4325</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2071</v>
+        <v>-0.0704</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6287</v>
+        <v>-0.3621</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.583</v>
+        <v>-1.5082</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0693</v>
+        <v>-1.8821</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4862</v>
+        <v>0.3739</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8077</v>
@@ -922,13 +922,13 @@
         <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3619</v>
+        <v>0.4368</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.132</v>
+        <v>0.0552</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4939</v>
+        <v>0.3816</v>
       </c>
       <c r="V6" t="n">
         <v>0.845</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. KOYANOUBA DJIRANGAYE</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0061</v>
+        <v>-2.3112</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.3434</v>
+        <v>-2.787</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3373</v>
+        <v>0.4758</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.2547</v>
+        <v>-1.8936</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9685</v>
+        <v>-2.8903</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.2862</v>
+        <v>0.9967</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.6786</v>
+        <v>-1.6473</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-1.6875</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.913</v>
+        <v>0.0402</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5761</v>
+        <v>-0.2463</v>
       </c>
       <c r="N7" t="n">
         <v>-1.2028</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3733</v>
+        <v>0.9565</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3964</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3787</v>
+        <v>0.5947</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8663</v>
+        <v>-0.0211</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1103</v>
+        <v>-0.1486</v>
       </c>
       <c r="U7" t="n">
-        <v>0.756</v>
+        <v>0.1275</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9858</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2213</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>E. KOYANOUBA DJIRANGAYE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1979</v>
+        <v>-2.5072</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6456</v>
+        <v>-3.5637</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4477</v>
+        <v>1.0565</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8936</v>
+        <v>-4.2547</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.8903</v>
+        <v>-1.9685</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9967</v>
+        <v>-2.2862</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.6473</v>
+        <v>-2.6786</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6875</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0402</v>
+        <v>-1.913</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2463</v>
+        <v>-1.5761</v>
       </c>
       <c r="N8" t="n">
         <v>-1.2028</v>
       </c>
       <c r="O8" t="n">
-        <v>0.9565</v>
+        <v>-0.3733</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3964</v>
+        <v>0.3964</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5947</v>
+        <v>2.3787</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0921</v>
+        <v>0.3652</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0072</v>
+        <v>-0.11</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0994</v>
+        <v>0.4752</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9858</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2213</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9119</v>
+        <v>-3.7539</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3272</v>
+        <v>-1.2253</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5848</v>
+        <v>-2.5286</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3759</v>
@@ -1156,13 +1156,13 @@
         <v>0.5947</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3993</v>
+        <v>-0.2413</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4368</v>
+        <v>-0.3349</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0374</v>
+        <v>0.0936</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7403</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.7667</v>
+        <v>-5.2021</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.7756</v>
+        <v>-5.4076</v>
       </c>
       <c r="F10" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.2055</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4141</v>
@@ -1234,13 +1234,13 @@
         <v>1.9822</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1721</v>
+        <v>-0.6075</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3103</v>
+        <v>-0.9423</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1383</v>
+        <v>0.3348</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2071</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-11.6758</v>
+        <v>-10.4281</v>
       </c>
       <c r="E11" t="n">
-        <v>-11.438</v>
+        <v>-10.1901</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2381000000000003</v>
+        <v>-0.2379999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3761</v>
@@ -1303,7 +1303,7 @@
         <v>1.5577</v>
       </c>
       <c r="P11" t="n">
-        <v>-4.9555</v>
+        <v>-4.955500000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>-17.84</v>
@@ -1312,10 +1312,10 @@
         <v>12.8846</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6152</v>
+        <v>-0.3671</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.9815</v>
+        <v>-2.7336</v>
       </c>
       <c r="U11" t="n">
         <v>2.3666</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>L. MORENO MORALES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.7999</v>
+        <v>4.2037</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8287</v>
+        <v>0.6102</v>
       </c>
       <c r="F12" t="n">
-        <v>2.9712</v>
+        <v>3.5935</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9363</v>
+        <v>0.3386</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7126</v>
+        <v>0.5029</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2237</v>
+        <v>-0.1643</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6921</v>
+        <v>0.2359</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4912</v>
+        <v>0.4174</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2009</v>
+        <v>-0.1814</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2442</v>
+        <v>0.1027</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2214</v>
+        <v>0.0856</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0228</v>
+        <v>0.0171</v>
       </c>
       <c r="P12" t="n">
-        <v>2.7751</v>
+        <v>0.9911</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1982</v>
+        <v>-1.9822</v>
       </c>
       <c r="R12" t="n">
         <v>2.9733</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5622</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3349</v>
+        <v>-0.5909</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2273</v>
+        <v>0.5174</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4737</v>
+        <v>2.9474</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.9474</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. MORENO MORALES</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7962</v>
+        <v>3.6959</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2027</v>
+        <v>0.8932</v>
       </c>
       <c r="F13" t="n">
-        <v>3.5935</v>
+        <v>2.8027</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3386</v>
+        <v>0.9363</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5029</v>
+        <v>0.7126</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1643</v>
+        <v>0.2237</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2359</v>
+        <v>0.6921</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4174</v>
+        <v>0.4912</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1814</v>
+        <v>0.2009</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1027</v>
+        <v>0.2442</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0856</v>
+        <v>0.2214</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0171</v>
+        <v>0.0228</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9911</v>
+        <v>2.7751</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9822</v>
+        <v>-0.1982</v>
       </c>
       <c r="R13" t="n">
         <v>2.9733</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4809</v>
+        <v>1.4582</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9984</v>
+        <v>0.3994</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5174</v>
+        <v>1.0589</v>
       </c>
       <c r="V13" t="n">
-        <v>2.9474</v>
+        <v>-1.4737</v>
       </c>
       <c r="W13" t="n">
-        <v>2.9474</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="14">
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1453</v>
+        <v>3.5527</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8592</v>
+        <v>1.2667</v>
       </c>
       <c r="F14" t="n">
         <v>2.2861</v>
@@ -1546,10 +1546,10 @@
         <v>1.5858</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7415</v>
+        <v>-0.334</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8112</v>
+        <v>-0.4037</v>
       </c>
       <c r="U14" t="n">
         <v>0.0696</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5922</v>
+        <v>2.27</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0658</v>
+        <v>0.4436</v>
       </c>
       <c r="F15" t="n">
-        <v>1.658</v>
+        <v>1.8265</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0502</v>
@@ -1624,13 +1624,13 @@
         <v>2.3787</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.754</v>
+        <v>-0.0762</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.4266</v>
       </c>
       <c r="U15" t="n">
-        <v>0.182</v>
+        <v>0.3504</v>
       </c>
       <c r="V15" t="n">
         <v>1.2071</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3005</v>
+        <v>1.1497</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2124</v>
+        <v>-1.1105</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5129</v>
+        <v>2.2602</v>
       </c>
       <c r="G16" t="n">
         <v>1.8985</v>
@@ -1702,13 +1702,13 @@
         <v>2.5769</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9878</v>
+        <v>0.8369</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3192</v>
+        <v>-0.2174</v>
       </c>
       <c r="U16" t="n">
-        <v>1.307</v>
+        <v>1.0543</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.873</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2378</v>
+        <v>2.0341</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3648</v>
+        <v>-1.2806</v>
       </c>
       <c r="G17" t="n">
         <v>0.3983</v>
@@ -1780,13 +1780,13 @@
         <v>0.5947</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.12</v>
+        <v>-0.2395</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2423</v>
+        <v>0.0386</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3624</v>
+        <v>-0.2781</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.079</v>
+        <v>-0.0437</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3549</v>
+        <v>-0.1511</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2759</v>
+        <v>0.1074</v>
       </c>
       <c r="G20" t="n">
         <v>-0.4777</v>
@@ -2014,13 +2014,13 @@
         <v>1.3876</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0528</v>
+        <v>0.0881</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5616</v>
+        <v>-0.3578</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6143999999999999</v>
+        <v>0.4459</v>
       </c>
       <c r="V20" t="n">
         <v>0.9405</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6129</v>
+        <v>-0.3811</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4075</v>
+        <v>0.6112</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0204</v>
+        <v>-0.9923</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9546</v>
@@ -2092,13 +2092,13 @@
         <v>0.5947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2529</v>
+        <v>-0.0211</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4368</v>
+        <v>-0.233</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1838</v>
+        <v>0.2119</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6701</v>
+        <v>-1.4279</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4999</v>
+        <v>-1.3981</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1702</v>
+        <v>-0.0298</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6309</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3652</v>
+        <v>-0.123</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1872</v>
+        <v>-0.0853</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1781</v>
+        <v>-0.0377</v>
       </c>
       <c r="V22" t="n">
         <v>-0.674</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6771</v>
+        <v>-3.3048</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3729</v>
+        <v>-4.1692</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6959</v>
+        <v>0.8643</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5229</v>
@@ -2248,13 +2248,13 @@
         <v>2.7751</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2731</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6936</v>
+        <v>-0.4899</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4205</v>
+        <v>0.589</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4846</v>
@@ -2284,10 +2284,10 @@
         <v>11.676</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2380000000000004</v>
+        <v>0.2381000000000011</v>
       </c>
       <c r="F24" t="n">
-        <v>11.4381</v>
+        <v>11.438</v>
       </c>
       <c r="G24" t="n">
         <v>4.376000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>17.8401</v>
       </c>
       <c r="S24" t="n">
-        <v>1.6152</v>
+        <v>1.6151</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.3668</v>
+        <v>-2.3666</v>
       </c>
       <c r="U24" t="n">
-        <v>3.9815</v>
+        <v>3.9816</v>
       </c>
       <c r="V24" t="n">
         <v>0.7293000000000003</v>
